--- a/shj/ShanHai_Data.xlsx
+++ b/shj/ShanHai_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ROG\Desktop\山海经\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F30B39-DB5F-46E7-B26C-D65CAE843987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D158EA4-B93A-4674-B1BC-3F2EAD89D85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Talents" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="451">
   <si>
     <t>TalentID</t>
   </si>
@@ -847,15 +847,6 @@
     <t>if(event==='onVision'){ if(self._cd1018===undefined) self._cd1018 = -999999; if(Game.tickCount - self._cd1018 &gt;= 1800){ let triggered = false; for(let i=Game.corpses.length-1; i&gt;=0; i--){ let cp=Game.corpses[i]; if(Math.hypot((cp.x+cp.cxOffset)-(self.x+self.cxOffset), (cp.y+cp.cyOffset)-(self.y+self.cyOffset)) &lt;= value){ Game.eatCorpse(self, cp, i); triggered = true; } } if(triggered) self._cd1018 = Game.tickCount; } } return value;</t>
   </si>
   <si>
-    <t>分身术</t>
-  </si>
-  <si>
-    <t>每隔30秒，召唤一个自身的复制，但没有任何天赋，生命只有自身30%，自身和分身不会相互攻击</t>
-  </si>
-  <si>
-    <t>if(event==='onVision'){ if(self._cd1024===undefined) self._cd1024 = -999999; if(Game.tickCount - self._cd1024 &gt;= 1800 &amp;&amp; self.enemyTarget){ let clone = JSON.parse(JSON.stringify(self)); clone.id = CreatureFactory.guid++; clone.maxHp = Math.floor(self.maxHp * 0.3); clone.hp = clone.maxHp; clone.talents = []; clone.x += (Math.random()&gt;0.5?1:-1); clone.y += (Math.random()&gt;0.5?1:-1); Game.creatures.push(clone); Game.addFloatingText(self.x, self.y, '分身!', '#a29bfe'); self._cd1024 = Game.tickCount; } } return value;</t>
-  </si>
-  <si>
     <t>每隔30秒，降下神雷，对全图所有除了传说外的敌人造成300%伤害</t>
   </si>
   <si>
@@ -1544,12 +1535,6 @@
     <t>回旋飞刃</t>
   </si>
   <si>
-    <t>十字爆破</t>
-  </si>
-  <si>
-    <t>攻击暴击时，在目标脚下产生一个十字形的爆炸，对目标周围的所有生物造成二次伤害。</t>
-  </si>
-  <si>
     <t>缓慢泥丸</t>
   </si>
   <si>
@@ -1644,10 +1629,6 @@
   </si>
   <si>
     <t>if(event==='onVision'){ if(self._cd1128===undefined) self._cd1128=-999999; if(Game.tickCount - self._cd1128 &gt;= 480){ let ce=null; let minD=Infinity; Game.creatures.forEach(c=&gt;{ if(c!==self &amp;&amp; !c._isDead){ let d=Math.hypot(c.x-self.x, c.y-self.y); if(d&lt;minD){ minD=d; ce=c; } }}); if(ce){ let sx=self.x+self.cxOffset, sy=self.y+self.cyOffset; let dx=ce.x+ce.cxOffset-sx, dy=ce.y+ce.cyOffset-sy; let dist=Math.hypot(dx,dy) || 0.1; Game.projectiles.push({ownerId: self.id, x:sx, y:sy, vx:(dx/dist)*2.5, vy:(dy/dist)*2.5, speed:2.5, traveled:0, maxDist:8000, damage:self.atk*2, color:'#dcdde1', boomerang:true, isReturning:false}); Game.addFloatingText(self.x, self.y, '回旋刃', '#dcdde1'); self._cd1128=Game.tickCount; } } } return value;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>if(event==='onAttack' &amp;&amp; Math.random()&lt;self.critRate &amp;&amp; target){ let ex=target.x+target.cxOffset, ey=target.y+target.cyOffset; let dmg=self.atk; [[0,-1],[0,1],[-1,0],[1,0]].forEach(dir=&gt;{ Game.projectiles.push({ownerId: self.id, x:ex, y:ey, vx:dir[0]*2, vy:dir[1]*2, speed:2, traveled:0, maxDist:1000, damage:dmg, color:'#e84118', pierce:true}); }); } return value;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2105,7 +2086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="62" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="11" style="9"/>
@@ -2399,7 +2380,7 @@
         <v>208</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="62" customHeight="1">
@@ -2522,1405 +2503,1405 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="62" customHeight="1" thickBot="1">
-      <c r="A25" s="9">
-        <v>1024</v>
+      <c r="A25" s="3">
+        <v>1025</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>214</v>
+        <v>87</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>215</v>
+        <v>126</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>216</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A26" s="3">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A27" s="3">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A28" s="3">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A29" s="3">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A30" s="3">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>34</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A31" s="3">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A32" s="3">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="62" customHeight="1" thickBot="1">
-      <c r="A33" s="3">
-        <v>1032</v>
+      <c r="A33" s="9">
+        <v>1033</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>131</v>
+        <v>214</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>124</v>
+        <v>215</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="62" customHeight="1" thickBot="1">
-      <c r="A34" s="9">
-        <v>1033</v>
+      <c r="A34" s="3">
+        <v>1034</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>217</v>
+        <v>132</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>218</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A35" s="3">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A36" s="3">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="62" customHeight="1" thickBot="1">
-      <c r="A37" s="3">
-        <v>1036</v>
+      <c r="A37" s="9">
+        <v>1037</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>134</v>
+        <v>216</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>125</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="62" customHeight="1" thickBot="1">
-      <c r="A38" s="9">
-        <v>1037</v>
+      <c r="A38" s="3">
+        <v>1038</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>219</v>
+        <v>135</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A39" s="3">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A40" s="3">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A41" s="3">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="62" customHeight="1" thickBot="1">
-      <c r="A42" s="3">
-        <v>1041</v>
+      <c r="A42" s="9">
+        <v>1042</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>138</v>
+        <v>218</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>115</v>
+        <v>219</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="62" customHeight="1" thickBot="1">
-      <c r="A43" s="9">
-        <v>1042</v>
+      <c r="A43" s="3">
+        <v>1043</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>34</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>221</v>
+        <v>139</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>222</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A44" s="3">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>34</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A45" s="3">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A46" s="3">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>119</v>
+        <v>183</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>143</v>
+        <v>182</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A47" s="3">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>183</v>
+        <v>145</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>169</v>
+        <v>205</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A48" s="3">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A49" s="3">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A50" s="3">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A51" s="3">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A52" s="3">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A53" s="3">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A54" s="3">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>29</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="62" customHeight="1" thickBot="1">
-      <c r="A55" s="3">
-        <v>1054</v>
+      <c r="A55" s="9">
+        <v>1055</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>184</v>
+        <v>220</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>176</v>
+        <v>221</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>154</v>
+        <v>222</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="62" customHeight="1" thickBot="1">
-      <c r="A56" s="9">
-        <v>1055</v>
+      <c r="A56" s="3">
+        <v>1056</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>223</v>
+        <v>155</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>224</v>
+        <v>186</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>225</v>
+        <v>156</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A57" s="3">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A58" s="3">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C58" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A59" s="3">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A60" s="3">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="C60" s="9" t="s">
         <v>29</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A61" s="3">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A62" s="3">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="62" customHeight="1" thickBot="1">
-      <c r="A63" s="3">
-        <v>1062</v>
+      <c r="A63" s="9">
+        <v>1063</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>164</v>
+        <v>224</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="62" customHeight="1" thickBot="1">
-      <c r="A64" s="9">
-        <v>1063</v>
+      <c r="A64" s="3">
+        <v>1064</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>227</v>
+        <v>196</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A65" s="3">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A66" s="3">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>34</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="62" customHeight="1" thickBot="1">
       <c r="A67" s="3">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="62" customHeight="1" thickBot="1">
-      <c r="A68" s="3">
-        <v>1067</v>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="62" customHeight="1">
+      <c r="A68" s="9">
+        <v>2001</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>29</v>
+        <v>227</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>202</v>
+        <v>273</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>204</v>
+        <v>274</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="62" customHeight="1">
       <c r="A69" s="9">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B69" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E69" s="9" t="s">
         <v>229</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="E69" s="9" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="62" customHeight="1">
       <c r="A70" s="9">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B70" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="E70" s="9" t="s">
         <v>231</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="E70" s="9" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="62" customHeight="1">
       <c r="A71" s="9">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B71" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="E71" s="9" t="s">
         <v>233</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="E71" s="9" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="62" customHeight="1">
       <c r="A72" s="9">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B72" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="E72" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="E72" s="9" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="62" customHeight="1">
       <c r="A73" s="9">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B73" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="E73" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="62" customHeight="1">
       <c r="A74" s="9">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B74" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="E74" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="E74" s="9" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="62" customHeight="1">
       <c r="A75" s="9">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B75" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="E75" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="C75" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="E75" s="9" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="62" customHeight="1">
       <c r="A76" s="9">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B76" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="E76" s="9" t="s">
         <v>243</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D76" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="E76" s="9" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="62" customHeight="1">
       <c r="A77" s="9">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B77" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="E77" s="9" t="s">
         <v>245</v>
-      </c>
-      <c r="C77" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="E77" s="9" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="62" customHeight="1">
       <c r="A78" s="9">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>248</v>
+        <v>285</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="62" customHeight="1">
       <c r="A79" s="9">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>288</v>
+        <v>248</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="62" customHeight="1">
       <c r="A80" s="9">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B80" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="E80" s="9" t="s">
         <v>250</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="E80" s="9" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="62" customHeight="1">
       <c r="A81" s="9">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B81" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="E81" s="9" t="s">
         <v>252</v>
-      </c>
-      <c r="C81" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="62" customHeight="1">
       <c r="A82" s="9">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B82" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="E82" s="9" t="s">
         <v>254</v>
-      </c>
-      <c r="C82" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="E82" s="9" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="62" customHeight="1">
       <c r="A83" s="9">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B83" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="E83" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="C83" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="E83" s="9" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="62" customHeight="1">
       <c r="A84" s="9">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B84" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="E84" s="9" t="s">
         <v>258</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="E84" s="9" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="62" customHeight="1">
       <c r="A85" s="9">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B85" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="E85" s="9" t="s">
         <v>260</v>
-      </c>
-      <c r="C85" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="E85" s="9" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="62" customHeight="1">
       <c r="A86" s="9">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B86" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="E86" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="C86" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D86" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="E86" s="9" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="62" customHeight="1">
       <c r="A87" s="9">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B87" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="E87" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="C87" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="E87" s="9" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="62" customHeight="1">
       <c r="A88" s="9">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B88" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="E88" s="9" t="s">
         <v>266</v>
-      </c>
-      <c r="C88" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="E88" s="9" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="62" customHeight="1">
       <c r="A89" s="9">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="B89" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="E89" s="9" t="s">
         <v>268</v>
-      </c>
-      <c r="C89" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="E89" s="9" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="62" customHeight="1">
       <c r="A90" s="9">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>271</v>
+        <v>350</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="62" customHeight="1">
       <c r="A91" s="9">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>353</v>
+        <v>271</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="62" customHeight="1">
       <c r="A92" s="9">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>274</v>
+        <v>354</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="62" customHeight="1">
       <c r="A93" s="9">
-        <v>2030</v>
+        <v>1085</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>275</v>
+        <v>355</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>230</v>
+        <v>37</v>
       </c>
       <c r="D93" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="E93" s="9" t="s">
         <v>356</v>
-      </c>
-      <c r="E93" s="9" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="62" customHeight="1">
       <c r="A94" s="9">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D94" s="9" t="s">
         <v>384</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="62" customHeight="1">
       <c r="A95" s="9">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B95" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="E95" s="9" t="s">
         <v>385</v>
-      </c>
-      <c r="C95" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="E95" s="9" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="62" customHeight="1">
       <c r="A96" s="9">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="62" customHeight="1">
       <c r="A97" s="9">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>389</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="62" customHeight="1">
       <c r="A98" s="9">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>363</v>
+        <v>391</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="62" customHeight="1">
       <c r="A99" s="9">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>394</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="62" customHeight="1">
       <c r="A100" s="9">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B100" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="C100" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="E100" s="9" t="s">
         <v>365</v>
-      </c>
-      <c r="C100" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="E100" s="9" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="62" customHeight="1">
       <c r="A101" s="9">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C101" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="62" customHeight="1">
       <c r="A102" s="9">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>397</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="62" customHeight="1">
       <c r="A103" s="9">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C103" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="62" customHeight="1">
       <c r="A104" s="9">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B104" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="C104" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="E104" s="9" t="s">
         <v>372</v>
-      </c>
-      <c r="C104" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="E104" s="9" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="62" customHeight="1">
       <c r="A105" s="9">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>401</v>
+        <v>373</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>375</v>
+        <v>400</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="62" customHeight="1">
       <c r="A106" s="9">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>403</v>
+        <v>374</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="62" customHeight="1">
       <c r="A107" s="9">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>405</v>
+        <v>375</v>
       </c>
       <c r="C107" s="9" t="s">
         <v>37</v>
@@ -3929,276 +3910,276 @@
         <v>404</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="62" customHeight="1">
       <c r="A108" s="9">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C108" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E108" s="9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="62" customHeight="1">
       <c r="A109" s="9">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>408</v>
+        <v>378</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="62" customHeight="1">
       <c r="A110" s="9">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B110" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="C110" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="E110" s="9" t="s">
         <v>380</v>
-      </c>
-      <c r="C110" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D110" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="E110" s="9" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="62" customHeight="1">
       <c r="A111" s="9">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>383</v>
+        <v>421</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="62" customHeight="1">
       <c r="A112" s="9">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E112" s="9" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="62" customHeight="1">
       <c r="A113" s="9">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="C113" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="62" customHeight="1">
       <c r="A114" s="9">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="62" customHeight="1">
       <c r="A115" s="9">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="62" customHeight="1">
       <c r="A116" s="9">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="E116" s="9" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="62" customHeight="1">
       <c r="A117" s="9">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="62" customHeight="1">
       <c r="A118" s="9">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D118" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="E118" s="9" t="s">
         <v>434</v>
-      </c>
-      <c r="E118" s="9" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="62" customHeight="1">
       <c r="A119" s="9">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>436</v>
+        <v>414</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>437</v>
+        <v>415</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="62" customHeight="1">
       <c r="A120" s="9">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C120" s="9" t="s">
         <v>34</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="E120" s="9" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="62" customHeight="1">
       <c r="A121" s="9">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="62" customHeight="1">
       <c r="A122" s="9">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>421</v>
+        <v>446</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="62" customHeight="1">
       <c r="A123" s="9">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>448</v>
+        <v>418</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>450</v>
@@ -4206,53 +4187,19 @@
     </row>
     <row r="124" spans="1:5" ht="62" customHeight="1">
       <c r="A124" s="9">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="62" customHeight="1">
-      <c r="A125" s="9">
-        <v>1133</v>
-      </c>
-      <c r="B125" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="C125" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D125" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="E125" s="9" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" ht="62" customHeight="1">
-      <c r="A126" s="9">
-        <v>1134</v>
-      </c>
-      <c r="B126" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="C126" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D126" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="E126" s="9" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -4308,7 +4255,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C2" s="2">
         <v>4</v>
@@ -4323,13 +4270,13 @@
         <v>100</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="J2" s="2">
         <v>2001</v>
@@ -4340,7 +4287,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C3" s="2">
         <v>4</v>
@@ -4358,10 +4305,10 @@
         <v>22</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J3" s="2">
         <v>2002</v>
@@ -4387,13 +4334,13 @@
         <v>80</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="J4" s="2">
         <v>2003</v>
@@ -4419,13 +4366,13 @@
         <v>50</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="J5" s="2">
         <v>2004</v>
@@ -4436,7 +4383,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C6" s="2">
         <v>3</v>
@@ -4451,13 +4398,13 @@
         <v>200</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="J6" s="2">
         <v>2005</v>
@@ -4468,7 +4415,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C7" s="2">
         <v>4</v>
@@ -4483,13 +4430,13 @@
         <v>150</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>305</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>308</v>
       </c>
       <c r="J7" s="2">
         <v>2006</v>
@@ -4500,7 +4447,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C8" s="2">
         <v>3</v>
@@ -4521,7 +4468,7 @@
         <v>23</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="J8" s="2">
         <v>2007</v>
@@ -4532,7 +4479,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C9" s="2">
         <v>2</v>
@@ -4547,13 +4494,13 @@
         <v>30</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J9" s="2">
         <v>2008</v>
@@ -4585,7 +4532,7 @@
         <v>21</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="J10" s="2">
         <v>2009</v>
@@ -4596,7 +4543,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C11" s="2">
         <v>4</v>
@@ -4611,13 +4558,13 @@
         <v>150</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="J11" s="2">
         <v>2010</v>
@@ -4628,7 +4575,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C12" s="2">
         <v>3</v>
@@ -4649,7 +4596,7 @@
         <v>26</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="J12" s="2">
         <v>2011</v>
@@ -4660,7 +4607,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C13" s="2">
         <v>3</v>
@@ -4675,13 +4622,13 @@
         <v>200</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="J13" s="2">
         <v>2013</v>
@@ -4692,7 +4639,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C14" s="2">
         <v>3</v>
@@ -4707,13 +4654,13 @@
         <v>50</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="J14" s="2">
         <v>2014</v>
@@ -4724,7 +4671,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C15" s="2">
         <v>4</v>
@@ -4739,13 +4686,13 @@
         <v>100</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J15" s="2">
         <v>2015</v>
@@ -4756,7 +4703,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C16" s="2">
         <v>3</v>
@@ -4771,13 +4718,13 @@
         <v>120</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="J16" s="2">
         <v>2016</v>
@@ -4788,7 +4735,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C17" s="2">
         <v>2</v>
@@ -4803,13 +4750,13 @@
         <v>40</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="J17" s="2">
         <v>2018</v>
@@ -4820,7 +4767,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C18" s="2">
         <v>4</v>
@@ -4835,13 +4782,13 @@
         <v>150</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="J18" s="2">
         <v>2020</v>
@@ -4852,7 +4799,7 @@
         <v>21</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C19" s="2">
         <v>3</v>
@@ -4867,13 +4814,13 @@
         <v>300</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="J19" s="2">
         <v>2021</v>
@@ -4884,7 +4831,7 @@
         <v>22</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
@@ -4899,13 +4846,13 @@
         <v>60</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="J20" s="2">
         <v>2022</v>
@@ -4916,7 +4863,7 @@
         <v>24</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C21" s="2">
         <v>2</v>
@@ -4931,13 +4878,13 @@
         <v>50</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="J21" s="2">
         <v>2024</v>
@@ -4948,7 +4895,7 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C22" s="2">
         <v>2</v>
@@ -4963,13 +4910,13 @@
         <v>100</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="J22" s="2">
         <v>2025</v>
@@ -4980,7 +4927,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C23" s="2">
         <v>3</v>
@@ -4995,13 +4942,13 @@
         <v>150</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="J23" s="2">
         <v>2027</v>
@@ -5012,7 +4959,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C24" s="2">
         <v>4</v>
@@ -5027,13 +4974,13 @@
         <v>100</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J24" s="2">
         <v>2028</v>
@@ -5044,7 +4991,7 @@
         <v>29</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C25" s="2">
         <v>3</v>
@@ -5059,13 +5006,13 @@
         <v>80</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="J25" s="2">
         <v>2029</v>
@@ -5076,7 +5023,7 @@
         <v>30</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C26" s="2">
         <v>2</v>
@@ -5091,13 +5038,13 @@
         <v>40</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="J26" s="2">
         <v>2030</v>

--- a/shj/ShanHai_Data.xlsx
+++ b/shj/ShanHai_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ROG\Desktop\山海经\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D158EA4-B93A-4674-B1BC-3F2EAD89D85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C48D8F3-7025-44FC-9484-228FACBA0B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1656,15 +1656,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>每隔5秒，发射一枚幽灵弹，穿透所有敌人，对命中的敌人造成伤害并把等量伤害化作生命回复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>if(event==='onVision'){ if(self._cd1134===undefined) self._cd1134=-999999; if(Game.tickCount - self._cd1134 &gt;= ,300){ let ce=null; let minD=Infinity; Game.creatures.forEach(c=&gt;{ if(c!==self &amp;&amp; !c._isDead){ let d=Math.hypot(c.x-self.x, c.y-self.y); if(d&lt;minD){ minD=d; ce=c; } }}); if(ce){ let sx=self.x+self.cxOffset, sy=self.y+self.cyOffset, dx=ce.x+ce.cxOffset-sx, dy=ce.y+ce.cyOffset-sy; let dist=Math.hypot(dx,dy) || 0.1; Game.projectiles.push({ownerId: self.id, x:sx, y:sy, vx:(dx/dist)*1.5, vy:(dy/dist)*1.5, speed:1.5, traveled:0, maxDist:10000, damage:Math.floor(self.atk*1.5), color:'#8e44ad', pierce:true, lifesteal:true}); Game.addFloatingText(self.x, self.y, '吸取', '#8e44ad'); self._cd1134=Game.tickCount; } } } return value;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>if(event==='onAttack' &amp;&amp; Math.random()&lt;0.15 &amp;&amp; target){ let sx=self.x+self.cxOffset, sy=self.y+self.cyOffset, ex=target.x+target.cxOffset, ey=target.y+target.cyOffset; let dx=ex-sx, dy=ey-sy; let dist=Math.hypot(dx,dy) || 0.1; for(let i=0; i&lt;3; i++){ setTimeout(()=&gt;{ Game.projectiles.push({ownerId: self.id, x:sx, y:sy, vx:(dx/dist)*2.5, vy:(dy/dist)*2.5, speed:2.5, traveled:0, maxDist:3000, damage:Math.floor(self.atk*0.5), color:'#e74c3c'}); }, i*100); } Game.addFloatingText(self.x, self.y, '连珠', '#e74c3c'); } return value;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>if(event==='onVision'){ if(self._cd1134===undefined) self._cd1134=-999999; if(Game.tickCount - self._cd1134 &gt;= 600){ let ce=null; let minD=Infinity; Game.creatures.forEach(c=&gt;{ if(c!==self &amp;&amp; !c._isDead){ let d=Math.hypot(c.x-self.x, c.y-self.y); if(d&lt;minD){ minD=d; ce=c; } }}); if(ce){ let sx=self.x+self.cxOffset; let sy=self.y+self.cyOffset; let dx=ce.x+ce.cxOffset-sx; let dy=ce.y+ce.cyOffset-sy; let dist=Math.hypot(dx,dy) || 0.1; Game.projectiles.push({ownerId: self.id, x:sx, y:sy, vx:(dx/dist)*1.5, vy:(dy/dist)*1.5, speed:1.5, traveled:0, maxDist:500, damage:Math.floor(self.atk*1.5), color:'#8e44ad', pierce:true, lifesteal:true}); Game.addFloatingText(self.x, self.y, '吸取', '#8e44ad'); self._cd1134=Game.tickCount; } } } return value;</t>
+  </si>
+  <si>
+    <t>每隔10秒，发射一枚幽灵弹，对命中的敌人造成伤害并把等量伤害化作生命回复给你</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4182,7 +4181,7 @@
         <v>447</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="62" customHeight="1">
@@ -4196,7 +4195,7 @@
         <v>34</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E124" s="9" t="s">
         <v>449</v>
